--- a/artfynd/A 3152-2022 artfynd.xlsx
+++ b/artfynd/A 3152-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3152-2022 artfynd.xlsx
+++ b/artfynd/A 3152-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98436674</v>
+        <v>98437017</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550811.9942021057</v>
+        <v>550650</v>
       </c>
       <c r="R2" t="n">
-        <v>6681728.927398137</v>
+        <v>6682158</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,12 +786,7 @@
         <v>98437200</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550596.0812491665</v>
+        <v>550597</v>
       </c>
       <c r="R3" t="n">
-        <v>6682137.276472023</v>
+        <v>6682137</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,60 +891,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98438123</v>
+        <v>98437268</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550871.4584056779</v>
+        <v>550630</v>
       </c>
       <c r="R4" t="n">
-        <v>6681634.975127632</v>
+        <v>6682092</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,60 +999,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98436593</v>
+        <v>98437250</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550795.2496981776</v>
+        <v>550618</v>
       </c>
       <c r="R5" t="n">
-        <v>6681717.777328269</v>
+        <v>6682127</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,51 +1113,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98437017</v>
+        <v>98436593</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550649.9676459744</v>
+        <v>550796</v>
       </c>
       <c r="R6" t="n">
-        <v>6682157.870730018</v>
+        <v>6681718</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1222,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98436946</v>
+        <v>98436674</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,16 +1258,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1309,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550655.1615493884</v>
+        <v>550812</v>
       </c>
       <c r="R7" t="n">
-        <v>6682070.120034037</v>
+        <v>6681729</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,15 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98437518</v>
+        <v>98436803</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550736.8251879164</v>
+        <v>550695</v>
       </c>
       <c r="R8" t="n">
-        <v>6681915.946778776</v>
+        <v>6681886</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,15 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98437977</v>
+        <v>98436831</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1486,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1553,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550880.5677923895</v>
+        <v>550678</v>
       </c>
       <c r="R9" t="n">
-        <v>6681694.650387281</v>
+        <v>6681920</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1588,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,15 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98437457</v>
+        <v>98436946</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1603,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1675,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550742.353779427</v>
+        <v>550655</v>
       </c>
       <c r="R10" t="n">
-        <v>6681947.284176982</v>
+        <v>6682070</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1710,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,15 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98436831</v>
+        <v>98437457</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1720,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1797,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550677.6219279971</v>
+        <v>550743</v>
       </c>
       <c r="R11" t="n">
-        <v>6681920.086247353</v>
+        <v>6681947</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1832,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,15 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98437825</v>
+        <v>98437518</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550841.0518199443</v>
+        <v>550737</v>
       </c>
       <c r="R12" t="n">
-        <v>6681748.188602963</v>
+        <v>6681916</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1954,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,15 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98437888</v>
+        <v>98437583</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,14 +1954,10 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2041,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550878.5384669948</v>
+        <v>550802</v>
       </c>
       <c r="R13" t="n">
-        <v>6681697.599488487</v>
+        <v>6681874</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2076,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,15 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98438032</v>
+        <v>98437595</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550845.7600182964</v>
+        <v>550813</v>
       </c>
       <c r="R14" t="n">
-        <v>6681695.654033511</v>
+        <v>6681870</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2198,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,15 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98438069</v>
+        <v>98437825</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2184,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2285,10 +2199,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550850.9583909622</v>
+        <v>550841</v>
       </c>
       <c r="R15" t="n">
-        <v>6681643.621779824</v>
+        <v>6681749</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2320,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2330,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,15 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98436803</v>
+        <v>98437888</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2301,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2407,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550694.9860234373</v>
+        <v>550879</v>
       </c>
       <c r="R16" t="n">
-        <v>6681886.585616929</v>
+        <v>6681698</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2442,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2452,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,15 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111821928</v>
+        <v>98437977</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2512,20 +2416,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brunnsjöberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550826</v>
+        <v>550881</v>
       </c>
       <c r="R17" t="n">
-        <v>6681726</v>
+        <v>6681695</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2549,12 +2463,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,15 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111821927</v>
+        <v>98438032</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,20 +2533,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brunnsjöberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550820</v>
+        <v>550845</v>
       </c>
       <c r="R18" t="n">
-        <v>6681733</v>
+        <v>6681695</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2651,12 +2580,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,15 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111821923</v>
+        <v>98438069</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,28 +2650,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brunnsjöberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550701</v>
+        <v>550851</v>
       </c>
       <c r="R19" t="n">
-        <v>6681909</v>
+        <v>6681644</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,12 +2697,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,7 +2721,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2794,15 +2739,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111821924</v>
+        <v>98438123</v>
       </c>
       <c r="B20" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,28 +2767,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brunnsjöberget, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550675</v>
+        <v>550871</v>
       </c>
       <c r="R20" t="n">
-        <v>6681937</v>
+        <v>6681634</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,12 +2814,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,7 +2838,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2905,15 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111821926</v>
+        <v>108443108</v>
       </c>
       <c r="B21" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,20 +2884,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brunnsjöberget, Dlr</t>
+          <t>Källbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550846</v>
+        <v>550860</v>
       </c>
       <c r="R21" t="n">
-        <v>6681625</v>
+        <v>6681775</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,12 +2926,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-04-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,6 +2965,509 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111821923</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brunnsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>550701</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6681910</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111821924</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brunnsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>550676</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6681937</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111821926</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brunnsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>550846</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6681625</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111821927</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brunnsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>550820</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6681733</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>111821928</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brunnsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>550826</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6681726</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3152-2022 artfynd.xlsx
+++ b/artfynd/A 3152-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437017</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437268</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437250</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98436593</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98436674</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98436803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98436831</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98436946</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437457</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437518</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437583</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437595</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2385,6 +2460,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437888</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98437977</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98438032</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,6 +2826,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98438069</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2853,6 +2948,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98438123</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2965,6 +3065,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108443108</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3071,6 +3176,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111821923</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3177,6 +3287,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111821924</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3274,6 +3389,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111821926</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3371,6 +3491,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111821927</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3468,8 +3593,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111821928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>